--- a/research/traditional_assets/database/data/czech_republic/czech_republic_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_financial_svcs_non_bank_insurance.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.351</v>
+        <v>0.0837</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.303</v>
+        <v>2.61</v>
       </c>
       <c r="L2">
-        <v>0.03594306049822064</v>
+        <v>0.4578947368421052</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,55 +630,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.373</v>
+        <v>0.616</v>
       </c>
       <c r="V2">
-        <v>0.003535545023696682</v>
+        <v>0.006247464503042597</v>
       </c>
       <c r="W2">
-        <v>0.002837078651685393</v>
+        <v>0.02281468531468531</v>
       </c>
       <c r="X2">
-        <v>0.03510288487171411</v>
+        <v>0.06900427026882247</v>
       </c>
       <c r="Y2">
-        <v>-0.03226580622002872</v>
+        <v>-0.04618958495413716</v>
       </c>
       <c r="Z2">
-        <v>0.04349171954805758</v>
+        <v>0.02088470543405379</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03160611554655793</v>
+        <v>0.05844516015103789</v>
       </c>
       <c r="AC2">
-        <v>-0.03160611554655793</v>
+        <v>-0.05844516015103789</v>
       </c>
       <c r="AD2">
-        <v>158.9</v>
+        <v>213.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>158.9</v>
+        <v>213.5</v>
       </c>
       <c r="AG2">
-        <v>158.527</v>
+        <v>212.884</v>
       </c>
       <c r="AH2">
-        <v>0.6009833585476552</v>
+        <v>0.6840756167894905</v>
       </c>
       <c r="AI2">
-        <v>0.5797154323239694</v>
+        <v>0.6788553259141494</v>
       </c>
       <c r="AJ2">
-        <v>0.6004196540505327</v>
+        <v>0.6834508353559091</v>
       </c>
       <c r="AK2">
-        <v>0.5791427224935793</v>
+        <v>0.6782250767799568</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.351</v>
+        <v>0.0837</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -719,10 +719,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0.303</v>
+        <v>2.61</v>
       </c>
       <c r="L3">
-        <v>0.03594306049822064</v>
+        <v>0.4578947368421052</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,55 +746,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.373</v>
+        <v>0.616</v>
       </c>
       <c r="V3">
-        <v>0.003535545023696682</v>
+        <v>0.006247464503042597</v>
       </c>
       <c r="W3">
-        <v>0.002837078651685393</v>
+        <v>0.02281468531468531</v>
       </c>
       <c r="X3">
-        <v>0.03510288487171411</v>
+        <v>0.06900427026882247</v>
       </c>
       <c r="Y3">
-        <v>-0.03226580622002872</v>
+        <v>-0.04618958495413716</v>
       </c>
       <c r="Z3">
-        <v>0.04349171954805758</v>
+        <v>0.02088470543405379</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03160611554655793</v>
+        <v>0.05844516015103789</v>
       </c>
       <c r="AC3">
-        <v>-0.03160611554655793</v>
+        <v>-0.05844516015103789</v>
       </c>
       <c r="AD3">
-        <v>158.9</v>
+        <v>213.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>158.9</v>
+        <v>213.5</v>
       </c>
       <c r="AG3">
-        <v>158.527</v>
+        <v>212.884</v>
       </c>
       <c r="AH3">
-        <v>0.6009833585476552</v>
+        <v>0.6840756167894905</v>
       </c>
       <c r="AI3">
-        <v>0.5797154323239694</v>
+        <v>0.6788553259141494</v>
       </c>
       <c r="AJ3">
-        <v>0.6004196540505327</v>
+        <v>0.6834508353559091</v>
       </c>
       <c r="AK3">
-        <v>0.5791427224935793</v>
+        <v>0.6782250767799568</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/czech_republic/czech_republic_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_financial_svcs_non_bank_insurance.xlsx
@@ -588,7 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0837</v>
+        <v>-0.178</v>
+      </c>
+      <c r="E2">
+        <v>-0.198</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2.61</v>
+        <v>3.04</v>
       </c>
       <c r="L2">
-        <v>0.4578947368421052</v>
+        <v>0.6755555555555556</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.616</v>
+        <v>0.959</v>
       </c>
       <c r="V2">
-        <v>0.006247464503042597</v>
+        <v>0.01116414435389988</v>
       </c>
       <c r="W2">
-        <v>0.02281468531468531</v>
+        <v>0.0300990099009901</v>
       </c>
       <c r="X2">
-        <v>0.06900427026882247</v>
+        <v>0.07748251944675617</v>
       </c>
       <c r="Y2">
-        <v>-0.04618958495413716</v>
+        <v>-0.04738350954576608</v>
       </c>
       <c r="Z2">
-        <v>0.02088470543405379</v>
+        <v>0.01433650648010093</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05844516015103789</v>
+        <v>0.05711023950181224</v>
       </c>
       <c r="AC2">
-        <v>-0.05844516015103789</v>
+        <v>-0.05711023950181224</v>
       </c>
       <c r="AD2">
-        <v>213.5</v>
+        <v>206.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>213.5</v>
+        <v>206.7</v>
       </c>
       <c r="AG2">
-        <v>212.884</v>
+        <v>205.741</v>
       </c>
       <c r="AH2">
-        <v>0.6840756167894905</v>
+        <v>0.7064251537935747</v>
       </c>
       <c r="AI2">
-        <v>0.6788553259141494</v>
+        <v>0.6508186397984885</v>
       </c>
       <c r="AJ2">
-        <v>0.6834508353559091</v>
+        <v>0.7054597947476521</v>
       </c>
       <c r="AK2">
-        <v>0.6782250767799568</v>
+        <v>0.6497610858985413</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0837</v>
+        <v>-0.178</v>
+      </c>
+      <c r="E3">
+        <v>-0.198</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -719,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2.61</v>
+        <v>3.04</v>
       </c>
       <c r="L3">
-        <v>0.4578947368421052</v>
+        <v>0.6755555555555556</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.616</v>
+        <v>0.959</v>
       </c>
       <c r="V3">
-        <v>0.006247464503042597</v>
+        <v>0.01116414435389988</v>
       </c>
       <c r="W3">
-        <v>0.02281468531468531</v>
+        <v>0.0300990099009901</v>
       </c>
       <c r="X3">
-        <v>0.06900427026882247</v>
+        <v>0.07748251944675617</v>
       </c>
       <c r="Y3">
-        <v>-0.04618958495413716</v>
+        <v>-0.04738350954576608</v>
       </c>
       <c r="Z3">
-        <v>0.02088470543405379</v>
+        <v>0.01433650648010093</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05844516015103789</v>
+        <v>0.05711023950181224</v>
       </c>
       <c r="AC3">
-        <v>-0.05844516015103789</v>
+        <v>-0.05711023950181224</v>
       </c>
       <c r="AD3">
-        <v>213.5</v>
+        <v>206.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>213.5</v>
+        <v>206.7</v>
       </c>
       <c r="AG3">
-        <v>212.884</v>
+        <v>205.741</v>
       </c>
       <c r="AH3">
-        <v>0.6840756167894905</v>
+        <v>0.7064251537935747</v>
       </c>
       <c r="AI3">
-        <v>0.6788553259141494</v>
+        <v>0.6508186397984885</v>
       </c>
       <c r="AJ3">
-        <v>0.6834508353559091</v>
+        <v>0.7054597947476521</v>
       </c>
       <c r="AK3">
-        <v>0.6782250767799568</v>
+        <v>0.6497610858985413</v>
       </c>
       <c r="AL3">
         <v>0</v>
